--- a/kaggle_results/T11-21-2025/results_v248.xlsx
+++ b/kaggle_results/T11-21-2025/results_v248.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.git_projs\MedicalQA\kaggle_results\T11-21-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apps\obsidian\Research\1.git_projs\MedicalQA\kaggle_results\T11-21-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A6EB5E-B1E9-4D8E-AD82-F36F27E5A25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F661C3-A2C3-49DE-A9CE-29E99A26F690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="291">
   <si>
     <t>Sample_ID</t>
   </si>
@@ -299,13 +299,6 @@
   </si>
   <si>
     <t>Làm gì để có thể cải thiện chức năng sinh hoạt của người bệnh?</t>
-  </si>
-  <si>
-    <t>- Chuyên viên vật lí trị liệu có thể hướng dẫn những bài tập an toàn, thích hợp. Để tăng cường sức mạnh, sự linh động, thăng bằng cũng như sự điều hợp của cơ thể. Những bài tập này cũng giúp duy trì sự linh hoạt tốt nhất có thể và có thể giảm nguy cơ té ngã.
-- Hơn nữa, khi có chỉ định sử dụng xe lăn hay nạng, các chuyên viên vật lí trị liệu sẽ hướng dẫn người bệnh cách sử dụng xe lăn và nạng sao cho đúng và an toàn.
-- Các nhà hoạt động trị liệu có thể hỗ trợ người bệnh, người nhà và người chăm sóc sử dụng những dụng cụ hỗ trợ như tay vịn xung quanh nhà và dụng cụ ăn uống thích hợp để cải thiện chức năng sinh hoạt của người bệnh.
-- Các chuyên viên âm ngữ trị liệu có thể giúp người bệnh cải thiện khả năng nói rõ ràng hơn, cũng như giúp cải thiện những vấn đề về nhai và nuốt.
-- Nhà tâm lí trị liệu có thể dùng những liệu pháp tâm lí, giúp người bệnh giải quyết những vấn đề về hành vi, tạo điều kiện giao tiếp hiệu quả giữa các thành viên trong gia đình.</t>
   </si>
   <si>
     <t>1. [Final Score: 1.0000] - Chuyên viên vật lí trị liệu có thể hướng dẫn những bài tập an toàn, thích hợp. Để tăng cường sức mạnh, sự linh động, thăng bằng cũng như sự điều hợp của cơ thể. Những bài tập này cũng giúp duy trì sự linh hoạt tốt nhất có thể và có thể giảm nguy cơ té ngã.
@@ -1187,6 +1180,16 @@
       </rPr>
       <t xml:space="preserve"> như: tinh dầu từ lá ổi, hoa ổi, quả ổi, pectin, tanin, tannin, và các vi khuẩn.</t>
     </r>
+  </si>
+  <si>
+    <t>.- Chuyên viên vật lí trị liệu có thể hướng dẫn những bài tập an toàn, thích hợp. Để tăng cường sức mạnh, sự linh động, thăng bằng cũng như sự điều hợp của cơ thể. Những bài tập này cũng giúp duy trì sự linh hoạt tốt nhất có thể và có thể giảm nguy cơ té ngã.
+- Hơn nữa, khi có chỉ định sử dụng xe lăn hay nạng, các chuyên viên vật lí trị liệu sẽ hướng dẫn người bệnh cách sử dụng xe lăn và nạng sao cho đúng và an toàn.
+- Các nhà hoạt động trị liệu có thể hỗ trợ người bệnh, người nhà và người chăm sóc sử dụng những dụng cụ hỗ trợ như tay vịn xung quanh nhà và dụng cụ ăn uống thích hợp để cải thiện chức năng sinh hoạt của người bệnh.
+- Các chuyên viên âm ngữ trị liệu có thể giúp người bệnh cải thiện khả năng nói rõ ràng hơn, cũng như giúp cải thiện những vấn đề về nhai và nuốt.
+- Nhà tâm lí trị liệu có thể dùng những liệu pháp tâm lí, giúp người bệnh giải quyết những vấn đề về hành vi, tạo điều kiện giao tiếp hiệu quả giữa các thành viên trong gia đình.</t>
+  </si>
+  <si>
+    <t>remove highlight full context</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1219,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1232,6 +1235,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1263,7 +1272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1272,9 +1281,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1579,13 +1591,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O51"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P51"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="7" max="7" width="56.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="56.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1626,7 +1638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1645,7 +1657,7 @@
       <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
       <c r="H2" t="s">
@@ -1667,11 +1679,11 @@
         <v>1</v>
       </c>
       <c r="O2">
-        <f>K2-N2</f>
+        <f t="shared" ref="O2:O33" si="0">K2-N2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1690,7 +1702,7 @@
       <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
       <c r="H3" t="s">
@@ -1706,17 +1718,17 @@
         <v>0.64059999999999995</v>
       </c>
       <c r="M3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N3">
         <v>0.65280000000000005</v>
       </c>
       <c r="O3">
-        <f>K3-N3</f>
+        <f t="shared" si="0"/>
         <v>-1.22000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1735,7 +1747,7 @@
       <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" t="s">
         <v>25</v>
       </c>
       <c r="H4" t="s">
@@ -1757,11 +1769,11 @@
         <v>0.66349999999999998</v>
       </c>
       <c r="O4">
-        <f>K4-N4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1780,7 +1792,7 @@
       <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" t="s">
         <v>30</v>
       </c>
       <c r="H5" t="s">
@@ -1796,17 +1808,17 @@
         <v>0.87629999999999997</v>
       </c>
       <c r="M5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N5">
         <v>0.92369999999999997</v>
       </c>
       <c r="O5">
-        <f>K5-N5</f>
+        <f t="shared" si="0"/>
         <v>-4.7399999999999998E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1825,7 +1837,7 @@
       <c r="F6" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" t="s">
         <v>35</v>
       </c>
       <c r="H6" t="s">
@@ -1841,17 +1853,17 @@
         <v>0.3407</v>
       </c>
       <c r="M6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N6">
         <v>0.31879999999999997</v>
       </c>
       <c r="O6">
-        <f>K6-N6</f>
+        <f t="shared" si="0"/>
         <v>2.1900000000000031E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="336" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="342.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1880,24 +1892,24 @@
         <v>42</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K7" s="2">
         <v>0.59450000000000003</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N7" s="2">
         <v>0.40939999999999999</v>
       </c>
       <c r="O7" s="2">
-        <f>K7-N7</f>
+        <f t="shared" si="0"/>
         <v>0.18510000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1916,7 +1928,7 @@
       <c r="F8" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" t="s">
         <v>45</v>
       </c>
       <c r="H8" t="s">
@@ -1938,11 +1950,11 @@
         <v>0.94279999999999997</v>
       </c>
       <c r="O8">
-        <f>K8-N8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1961,7 +1973,7 @@
       <c r="F9" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" t="s">
         <v>50</v>
       </c>
       <c r="H9" t="s">
@@ -1977,17 +1989,17 @@
         <v>0.58050000000000002</v>
       </c>
       <c r="M9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N9">
         <v>0.57299999999999995</v>
       </c>
       <c r="O9">
-        <f>K9-N9</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000622E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2006,7 +2018,7 @@
       <c r="F10" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" t="s">
         <v>55</v>
       </c>
       <c r="H10" t="s">
@@ -2022,17 +2034,17 @@
         <v>0.43330000000000002</v>
       </c>
       <c r="M10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N10">
         <v>0.43340000000000001</v>
       </c>
       <c r="O10">
-        <f>K10-N10</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999988987E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2051,7 +2063,7 @@
       <c r="F11" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" t="s">
         <v>60</v>
       </c>
       <c r="H11" t="s">
@@ -2073,11 +2085,11 @@
         <v>0.72629999999999995</v>
       </c>
       <c r="O11">
-        <f>K11-N11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2096,7 +2108,7 @@
       <c r="F12" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" t="s">
         <v>65</v>
       </c>
       <c r="H12" t="s">
@@ -2118,57 +2130,60 @@
         <v>0.65090000000000003</v>
       </c>
       <c r="O12">
-        <f>K12-N12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="280" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5">
+    <row r="13" spans="1:16" ht="331.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4">
         <v>874</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="C13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>68</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="J13" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K13" s="5">
+      <c r="K13" s="4">
         <v>0.36770000000000003</v>
       </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="N13" s="5">
+      <c r="L13" s="4"/>
+      <c r="M13" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="N13" s="4">
         <v>0.52900000000000003</v>
       </c>
-      <c r="O13" s="5">
-        <f>K13-N13</f>
+      <c r="O13" s="4">
+        <f t="shared" si="0"/>
         <v>-0.1613</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2182,38 +2197,38 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" t="s">
         <v>73</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s">
         <v>75</v>
       </c>
-      <c r="H14" t="s">
-        <v>74</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>76</v>
-      </c>
-      <c r="J14" t="s">
-        <v>77</v>
       </c>
       <c r="K14">
         <v>0.97250000000000003</v>
       </c>
       <c r="M14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
       <c r="O14">
-        <f>K14-N14</f>
+        <f t="shared" si="0"/>
         <v>-2.7499999999999969E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2227,38 +2242,38 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s">
         <v>78</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" t="s">
         <v>80</v>
       </c>
-      <c r="H15" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>81</v>
-      </c>
-      <c r="J15" t="s">
-        <v>82</v>
       </c>
       <c r="K15">
         <v>0.89639999999999997</v>
       </c>
       <c r="M15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N15">
         <v>0.91369999999999996</v>
       </c>
       <c r="O15">
-        <f>K15-N15</f>
+        <f t="shared" si="0"/>
         <v>-1.7299999999999982E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2272,38 +2287,38 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" t="s">
         <v>83</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>84</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" t="s">
         <v>85</v>
       </c>
-      <c r="H16" t="s">
-        <v>84</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>86</v>
-      </c>
-      <c r="J16" t="s">
-        <v>87</v>
       </c>
       <c r="K16">
         <v>0.90559999999999996</v>
       </c>
       <c r="M16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N16">
         <v>0.9395</v>
       </c>
       <c r="O16">
-        <f>K16-N16</f>
+        <f t="shared" si="0"/>
         <v>-3.3900000000000041E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2317,83 +2332,86 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" t="s">
         <v>88</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I17" t="s">
         <v>90</v>
       </c>
-      <c r="H17" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" t="s">
-        <v>91</v>
-      </c>
       <c r="J17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
       <c r="O17">
-        <f>K17-N17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="18" spans="1:16" s="6" customFormat="1" ht="345.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="6">
         <v>621</v>
       </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="C18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="H18" t="s">
-        <v>93</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="J18" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="J18" t="s">
-        <v>96</v>
-      </c>
-      <c r="K18">
+      <c r="K18" s="6">
         <v>0.7288</v>
       </c>
-      <c r="M18" t="s">
-        <v>275</v>
-      </c>
-      <c r="N18">
+      <c r="M18" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="N18" s="6">
         <v>0.83440000000000003</v>
       </c>
-      <c r="O18">
-        <f>K18-N18</f>
+      <c r="O18" s="6">
+        <f t="shared" si="0"/>
         <v>-0.10560000000000003</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2407,83 +2425,83 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" t="s">
         <v>97</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" t="s">
         <v>99</v>
       </c>
-      <c r="H19" t="s">
-        <v>98</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>100</v>
-      </c>
-      <c r="J19" t="s">
-        <v>101</v>
       </c>
       <c r="K19">
         <v>0.76729999999999998</v>
       </c>
       <c r="M19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N19">
         <v>0.76729999999999998</v>
       </c>
       <c r="O19">
-        <f>K19-N19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="20" spans="1:16" s="6" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="6">
         <v>595</v>
       </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="C20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="H20" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="H20" t="s">
-        <v>103</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="J20" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="J20" t="s">
-        <v>106</v>
-      </c>
-      <c r="K20">
+      <c r="K20" s="6">
         <v>0.29199999999999998</v>
       </c>
-      <c r="M20" t="s">
-        <v>276</v>
-      </c>
-      <c r="N20">
+      <c r="M20" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="N20" s="6">
         <v>0.70430000000000004</v>
       </c>
-      <c r="O20">
-        <f>K20-N20</f>
+      <c r="O20" s="6">
+        <f t="shared" si="0"/>
         <v>-0.41230000000000006</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2497,38 +2515,38 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" t="s">
         <v>107</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>108</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="H21" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" t="s">
         <v>109</v>
       </c>
-      <c r="H21" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>110</v>
-      </c>
-      <c r="J21" t="s">
-        <v>111</v>
       </c>
       <c r="K21">
         <v>0.50560000000000005</v>
       </c>
       <c r="M21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N21">
         <v>0.52100000000000002</v>
       </c>
       <c r="O21">
-        <f>K21-N21</f>
+        <f t="shared" si="0"/>
         <v>-1.5399999999999969E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2542,38 +2560,38 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" t="s">
         <v>112</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>113</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" t="s">
         <v>114</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>115</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>116</v>
-      </c>
-      <c r="J22" t="s">
-        <v>117</v>
       </c>
       <c r="K22">
         <v>0.70130000000000003</v>
       </c>
       <c r="M22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N22">
         <v>0.69210000000000005</v>
       </c>
       <c r="O22">
-        <f>K22-N22</f>
+        <f t="shared" si="0"/>
         <v>9.199999999999986E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2587,38 +2605,38 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" t="s">
         <v>118</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>119</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" t="s">
         <v>120</v>
       </c>
-      <c r="H23" t="s">
-        <v>119</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>121</v>
-      </c>
-      <c r="J23" t="s">
-        <v>122</v>
       </c>
       <c r="K23">
         <v>0.50129999999999997</v>
       </c>
       <c r="M23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N23">
         <v>0.50129999999999997</v>
       </c>
       <c r="O23">
-        <f>K23-N23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2632,38 +2650,38 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" t="s">
         <v>123</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>124</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="H24" t="s">
+        <v>123</v>
+      </c>
+      <c r="I24" t="s">
         <v>125</v>
       </c>
-      <c r="H24" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>126</v>
-      </c>
-      <c r="J24" t="s">
-        <v>127</v>
       </c>
       <c r="K24">
         <v>0.53800000000000003</v>
       </c>
       <c r="M24" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N24">
         <v>0.54049999999999998</v>
       </c>
       <c r="O24">
-        <f>K24-N24</f>
+        <f t="shared" si="0"/>
         <v>-2.4999999999999467E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2677,38 +2695,38 @@
         <v>12</v>
       </c>
       <c r="E25" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" t="s">
         <v>128</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>129</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="H25" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" t="s">
         <v>130</v>
       </c>
-      <c r="H25" t="s">
-        <v>129</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>131</v>
-      </c>
-      <c r="J25" t="s">
-        <v>132</v>
       </c>
       <c r="K25">
         <v>0.82479999999999998</v>
       </c>
       <c r="M25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N25">
         <v>1</v>
       </c>
       <c r="O25">
-        <f>K25-N25</f>
+        <f t="shared" si="0"/>
         <v>-0.17520000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2722,38 +2740,38 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" t="s">
         <v>133</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>134</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="H26" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" t="s">
         <v>135</v>
       </c>
-      <c r="H26" t="s">
-        <v>134</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>136</v>
-      </c>
-      <c r="J26" t="s">
-        <v>137</v>
       </c>
       <c r="K26">
         <v>0.6159</v>
       </c>
       <c r="M26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N26">
         <v>0.71099999999999997</v>
       </c>
       <c r="O26">
-        <f>K26-N26</f>
+        <f t="shared" si="0"/>
         <v>-9.5099999999999962E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2767,38 +2785,38 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27" t="s">
         <v>138</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>139</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="H27" t="s">
         <v>140</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>141</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>142</v>
-      </c>
-      <c r="J27" t="s">
-        <v>143</v>
       </c>
       <c r="K27">
         <v>0.82099999999999995</v>
       </c>
       <c r="M27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N27">
         <v>1</v>
       </c>
       <c r="O27">
-        <f>K27-N27</f>
+        <f t="shared" si="0"/>
         <v>-0.17900000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2812,38 +2830,38 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" t="s">
         <v>144</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>145</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="H28" t="s">
         <v>146</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>147</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>148</v>
-      </c>
-      <c r="J28" t="s">
-        <v>149</v>
       </c>
       <c r="K28">
         <v>0.22869999999999999</v>
       </c>
       <c r="M28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N28">
         <v>0.22869999999999999</v>
       </c>
       <c r="O28">
-        <f>K28-N28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2857,38 +2875,38 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" t="s">
         <v>150</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>151</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="H29" t="s">
+        <v>150</v>
+      </c>
+      <c r="I29" t="s">
         <v>152</v>
       </c>
-      <c r="H29" t="s">
-        <v>151</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>153</v>
-      </c>
-      <c r="J29" t="s">
-        <v>154</v>
       </c>
       <c r="K29">
         <v>0.67800000000000005</v>
       </c>
       <c r="M29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N29">
         <v>0.73860000000000003</v>
       </c>
       <c r="O29">
-        <f>K29-N29</f>
+        <f t="shared" si="0"/>
         <v>-6.0599999999999987E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2902,38 +2920,38 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
+        <v>154</v>
+      </c>
+      <c r="F30" t="s">
         <v>155</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>156</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="H30" t="s">
+        <v>155</v>
+      </c>
+      <c r="I30" t="s">
         <v>157</v>
       </c>
-      <c r="H30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>158</v>
-      </c>
-      <c r="J30" t="s">
-        <v>159</v>
       </c>
       <c r="K30">
         <v>0.84950000000000003</v>
       </c>
       <c r="M30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N30">
         <v>0.84950000000000003</v>
       </c>
       <c r="O30">
-        <f>K30-N30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2947,38 +2965,38 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" t="s">
         <v>160</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="H31" t="s">
+        <v>160</v>
+      </c>
+      <c r="I31" t="s">
         <v>162</v>
       </c>
-      <c r="H31" t="s">
-        <v>161</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>163</v>
-      </c>
-      <c r="J31" t="s">
-        <v>164</v>
       </c>
       <c r="K31">
         <v>0.93489999999999995</v>
       </c>
       <c r="M31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N31">
         <v>0.82379999999999998</v>
       </c>
       <c r="O31">
-        <f>K31-N31</f>
+        <f t="shared" si="0"/>
         <v>0.11109999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2992,38 +3010,38 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" t="s">
         <v>165</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>166</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="H32" t="s">
+        <v>165</v>
+      </c>
+      <c r="I32" t="s">
         <v>167</v>
       </c>
-      <c r="H32" t="s">
-        <v>166</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>168</v>
-      </c>
-      <c r="J32" t="s">
-        <v>169</v>
       </c>
       <c r="K32">
         <v>0.54559999999999997</v>
       </c>
       <c r="M32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N32">
         <v>0.54559999999999997</v>
       </c>
       <c r="O32">
-        <f>K32-N32</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3037,38 +3055,38 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
+        <v>169</v>
+      </c>
+      <c r="F33" t="s">
         <v>170</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>171</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="H33" t="s">
+        <v>170</v>
+      </c>
+      <c r="I33" t="s">
         <v>172</v>
       </c>
-      <c r="H33" t="s">
-        <v>171</v>
-      </c>
-      <c r="I33" t="s">
-        <v>173</v>
-      </c>
       <c r="J33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K33">
         <v>1</v>
       </c>
       <c r="M33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N33">
         <v>1</v>
       </c>
       <c r="O33">
-        <f>K33-N33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3082,38 +3100,38 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" t="s">
         <v>174</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>175</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="H34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I34" t="s">
         <v>176</v>
       </c>
-      <c r="H34" t="s">
-        <v>175</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>177</v>
-      </c>
-      <c r="J34" t="s">
-        <v>178</v>
       </c>
       <c r="K34">
         <v>0.87560000000000004</v>
       </c>
       <c r="M34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N34">
         <v>0.87560000000000004</v>
       </c>
       <c r="O34">
-        <f>K34-N34</f>
+        <f t="shared" ref="O34:O65" si="1">K34-N34</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3127,38 +3145,38 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
+        <v>178</v>
+      </c>
+      <c r="F35" t="s">
         <v>179</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>180</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" t="s">
+        <v>179</v>
+      </c>
+      <c r="I35" t="s">
         <v>181</v>
       </c>
-      <c r="H35" t="s">
-        <v>180</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>182</v>
-      </c>
-      <c r="J35" t="s">
-        <v>183</v>
       </c>
       <c r="K35">
         <v>0.86080000000000001</v>
       </c>
       <c r="M35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N35">
         <v>0.81499999999999995</v>
       </c>
       <c r="O35">
-        <f>K35-N35</f>
+        <f t="shared" si="1"/>
         <v>4.5800000000000063E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3172,38 +3190,38 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F36" t="s">
         <v>184</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="H36" t="s">
+        <v>184</v>
+      </c>
+      <c r="I36" t="s">
         <v>186</v>
       </c>
-      <c r="H36" t="s">
-        <v>185</v>
-      </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>187</v>
-      </c>
-      <c r="J36" t="s">
-        <v>188</v>
       </c>
       <c r="K36">
         <v>0.38990000000000002</v>
       </c>
       <c r="M36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N36">
         <v>0.38990000000000002</v>
       </c>
       <c r="O36">
-        <f>K36-N36</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3217,38 +3235,38 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
+        <v>188</v>
+      </c>
+      <c r="F37" t="s">
         <v>189</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>190</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="H37" t="s">
+        <v>189</v>
+      </c>
+      <c r="I37" t="s">
         <v>191</v>
       </c>
-      <c r="H37" t="s">
-        <v>190</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>192</v>
-      </c>
-      <c r="J37" t="s">
-        <v>193</v>
       </c>
       <c r="K37">
         <v>0.7984</v>
       </c>
       <c r="M37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N37">
         <v>0.7984</v>
       </c>
       <c r="O37">
-        <f>K37-N37</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3262,38 +3280,38 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
+        <v>193</v>
+      </c>
+      <c r="F38" t="s">
         <v>194</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>195</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="H38" t="s">
         <v>196</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>197</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>198</v>
-      </c>
-      <c r="J38" t="s">
-        <v>199</v>
       </c>
       <c r="K38">
         <v>0.45219999999999999</v>
       </c>
       <c r="M38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N38">
         <v>0.45219999999999999</v>
       </c>
       <c r="O38">
-        <f>K38-N38</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3307,38 +3325,38 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
+        <v>199</v>
+      </c>
+      <c r="F39" t="s">
         <v>200</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>201</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="H39" t="s">
         <v>202</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>203</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>204</v>
-      </c>
-      <c r="J39" t="s">
-        <v>205</v>
       </c>
       <c r="K39">
         <v>0.75580000000000003</v>
       </c>
       <c r="M39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N39">
         <v>0.75580000000000003</v>
       </c>
       <c r="O39">
-        <f>K39-N39</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3352,38 +3370,38 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
+        <v>205</v>
+      </c>
+      <c r="F40" t="s">
         <v>206</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>207</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="H40" t="s">
+        <v>206</v>
+      </c>
+      <c r="I40" t="s">
         <v>208</v>
       </c>
-      <c r="H40" t="s">
-        <v>207</v>
-      </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>209</v>
-      </c>
-      <c r="J40" t="s">
-        <v>210</v>
       </c>
       <c r="K40">
         <v>0.23769999999999999</v>
       </c>
       <c r="M40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N40">
         <v>0.23769999999999999</v>
       </c>
       <c r="O40">
-        <f>K40-N40</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3397,38 +3415,38 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" t="s">
         <v>211</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>212</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="H41" t="s">
+        <v>211</v>
+      </c>
+      <c r="I41" t="s">
         <v>213</v>
       </c>
-      <c r="H41" t="s">
-        <v>212</v>
-      </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>214</v>
-      </c>
-      <c r="J41" t="s">
-        <v>215</v>
       </c>
       <c r="K41">
         <v>0.39419999999999999</v>
       </c>
       <c r="M41" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N41">
         <v>0.50670000000000004</v>
       </c>
       <c r="O41">
-        <f>K41-N41</f>
+        <f t="shared" si="1"/>
         <v>-0.11250000000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3442,38 +3460,38 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
+        <v>215</v>
+      </c>
+      <c r="F42" t="s">
         <v>216</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>217</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="H42" t="s">
+        <v>216</v>
+      </c>
+      <c r="I42" t="s">
         <v>218</v>
       </c>
-      <c r="H42" t="s">
-        <v>217</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>219</v>
-      </c>
-      <c r="J42" t="s">
-        <v>220</v>
       </c>
       <c r="K42">
         <v>0.68779999999999997</v>
       </c>
       <c r="M42" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N42">
         <v>0.72760000000000002</v>
       </c>
       <c r="O42">
-        <f>K42-N42</f>
+        <f t="shared" si="1"/>
         <v>-3.9800000000000058E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3487,38 +3505,38 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
+        <v>220</v>
+      </c>
+      <c r="F43" t="s">
         <v>221</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>222</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="H43" t="s">
         <v>223</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>224</v>
       </c>
-      <c r="I43" t="s">
-        <v>225</v>
-      </c>
       <c r="J43" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K43">
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N43">
         <v>1</v>
       </c>
       <c r="O43">
-        <f>K43-N43</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3532,38 +3550,38 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
+        <v>225</v>
+      </c>
+      <c r="F44" t="s">
         <v>226</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>227</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="H44" t="s">
+        <v>226</v>
+      </c>
+      <c r="I44" t="s">
         <v>228</v>
       </c>
-      <c r="H44" t="s">
-        <v>227</v>
-      </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>229</v>
-      </c>
-      <c r="J44" t="s">
-        <v>230</v>
       </c>
       <c r="K44">
         <v>0.77500000000000002</v>
       </c>
       <c r="M44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N44">
         <v>0.77500000000000002</v>
       </c>
       <c r="O44">
-        <f>K44-N44</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3577,38 +3595,38 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
+        <v>230</v>
+      </c>
+      <c r="F45" t="s">
         <v>231</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>232</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="H45" t="s">
+        <v>231</v>
+      </c>
+      <c r="I45" t="s">
         <v>233</v>
       </c>
-      <c r="H45" t="s">
-        <v>232</v>
-      </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>234</v>
-      </c>
-      <c r="J45" t="s">
-        <v>235</v>
       </c>
       <c r="K45">
         <v>0.96740000000000004</v>
       </c>
       <c r="M45" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N45">
         <v>0.96740000000000004</v>
       </c>
       <c r="O45">
-        <f>K45-N45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3622,38 +3640,38 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F46" t="s">
         <v>236</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>237</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="H46" t="s">
+        <v>236</v>
+      </c>
+      <c r="I46" t="s">
         <v>238</v>
       </c>
-      <c r="H46" t="s">
-        <v>237</v>
-      </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>239</v>
-      </c>
-      <c r="J46" t="s">
-        <v>240</v>
       </c>
       <c r="K46">
         <v>0.66279999999999994</v>
       </c>
       <c r="M46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N46">
         <v>0.56889999999999996</v>
       </c>
       <c r="O46">
-        <f>K46-N46</f>
+        <f t="shared" si="1"/>
         <v>9.3899999999999983E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3667,38 +3685,38 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
+        <v>240</v>
+      </c>
+      <c r="F47" t="s">
         <v>241</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>242</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" t="s">
+        <v>241</v>
+      </c>
+      <c r="I47" t="s">
         <v>243</v>
       </c>
-      <c r="H47" t="s">
-        <v>242</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>244</v>
-      </c>
-      <c r="J47" t="s">
-        <v>245</v>
       </c>
       <c r="K47">
         <v>0.77549999999999997</v>
       </c>
       <c r="M47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N47">
         <v>0.88</v>
       </c>
       <c r="O47">
-        <f>K47-N47</f>
+        <f t="shared" si="1"/>
         <v>-0.10450000000000004</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>46</v>
       </c>
@@ -3712,38 +3730,38 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
+        <v>245</v>
+      </c>
+      <c r="F48" t="s">
         <v>246</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>247</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="H48" t="s">
+        <v>246</v>
+      </c>
+      <c r="I48" t="s">
         <v>248</v>
       </c>
-      <c r="H48" t="s">
-        <v>247</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>249</v>
-      </c>
-      <c r="J48" t="s">
-        <v>250</v>
       </c>
       <c r="K48">
         <v>0.66510000000000002</v>
       </c>
       <c r="M48" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N48">
         <v>0.66510000000000002</v>
       </c>
       <c r="O48">
-        <f>K48-N48</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>47</v>
       </c>
@@ -3757,38 +3775,38 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
+        <v>250</v>
+      </c>
+      <c r="F49" t="s">
         <v>251</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>252</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="H49" t="s">
+        <v>251</v>
+      </c>
+      <c r="I49" t="s">
         <v>253</v>
       </c>
-      <c r="H49" t="s">
-        <v>252</v>
-      </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>254</v>
-      </c>
-      <c r="J49" t="s">
-        <v>255</v>
       </c>
       <c r="K49">
         <v>0.64019999999999999</v>
       </c>
       <c r="M49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N49">
         <v>1</v>
       </c>
       <c r="O49">
-        <f>K49-N49</f>
+        <f t="shared" si="1"/>
         <v>-0.35980000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>48</v>
       </c>
@@ -3802,38 +3820,38 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
+        <v>255</v>
+      </c>
+      <c r="F50" t="s">
         <v>256</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>257</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="H50" t="s">
+        <v>256</v>
+      </c>
+      <c r="I50" t="s">
         <v>258</v>
       </c>
-      <c r="H50" t="s">
-        <v>257</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>259</v>
-      </c>
-      <c r="J50" t="s">
-        <v>260</v>
       </c>
       <c r="K50">
         <v>0.67479999999999996</v>
       </c>
       <c r="M50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N50">
         <v>0.60829999999999995</v>
       </c>
       <c r="O50">
-        <f>K50-N50</f>
+        <f t="shared" si="1"/>
         <v>6.6500000000000004E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>49</v>
       </c>
@@ -3847,34 +3865,34 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
+        <v>260</v>
+      </c>
+      <c r="F51" t="s">
         <v>261</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>262</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="H51" t="s">
         <v>263</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>264</v>
       </c>
-      <c r="I51" t="s">
-        <v>265</v>
-      </c>
       <c r="J51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K51">
         <v>0.99980000000000002</v>
       </c>
       <c r="M51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N51">
         <v>0.99980000000000002</v>
       </c>
       <c r="O51">
-        <f>K51-N51</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
